--- a/exports/OIL_full_report.xlsx
+++ b/exports/OIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>150.55</v>
+        <v>146.5</v>
       </c>
       <c r="I2" t="n">
         <v>146.8916532123792</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K2" t="n">
-        <v>2.66</v>
+        <v>-0.1</v>
       </c>
       <c r="L2" t="n">
         <v>3.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.96</v>
+        <v>1.79</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.79</v>
       </c>
       <c r="O2" t="n">
         <v>0.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>7.02</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>149.5</v>
+        <v>163.45</v>
       </c>
       <c r="I3" t="n">
         <v>156.7833123368115</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.05</v>
+        <v>-11.57</v>
       </c>
       <c r="L3" t="n">
-        <v>3.52</v>
+        <v>12.18</v>
       </c>
       <c r="M3" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.17</v>
+        <v>9.06</v>
       </c>
       <c r="O3" t="n">
         <v>-2.79</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>12.17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>154.15</v>
+        <v>149.8</v>
       </c>
       <c r="I4" t="n">
         <v>152.609977775571</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.69</v>
+        <v>-8.35</v>
       </c>
       <c r="L4" t="n">
-        <v>6.79</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>2.27</v>
       </c>
       <c r="N4" t="n">
         <v>3.02</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44690.38541666666</v>
+        <v>44690.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>154.95</v>
+        <v>158</v>
       </c>
       <c r="I5" t="n">
         <v>157.9513863117792</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.44</v>
+        <v>-5.47</v>
       </c>
       <c r="L5" t="n">
         <v>11.68</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.73</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44691.55208333334</v>
+        <v>44692.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>144.65</v>
+        <v>142.85</v>
       </c>
       <c r="I6" t="n">
         <v>144.2093198802362</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.449999999999999</v>
+        <v>-9.59</v>
       </c>
       <c r="L6" t="n">
-        <v>9.779999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="M6" t="n">
         <v>1.39</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>10.67</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>149.25</v>
+        <v>163.35</v>
       </c>
       <c r="I7" t="n">
         <v>158.0865058073078</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.48</v>
+        <v>-14.35</v>
       </c>
       <c r="L7" t="n">
-        <v>5.71</v>
+        <v>14.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>2.32</v>
+        <v>7.64</v>
       </c>
       <c r="O7" t="n">
         <v>2.32</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>178.85</v>
+        <v>171.35</v>
       </c>
       <c r="I8" t="n">
         <v>175.1611575224268</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>9.49</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>12.03</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>18.9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44763.38541666666</v>
+        <v>44763.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>133.1</v>
+        <v>133.65</v>
       </c>
       <c r="I9" t="n">
         <v>133.4645682232232</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>22.32</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>7.7</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44818.55208333334</v>
+        <v>44819.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>128.6</v>
+        <v>126.05</v>
       </c>
       <c r="I10" t="n">
         <v>126.9388830104551</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>55</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.78</v>
+        <v>-5.69</v>
       </c>
       <c r="L10" t="n">
         <v>9.130000000000001</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.58</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>120.05</v>
+        <v>122.35</v>
       </c>
       <c r="I11" t="n">
         <v>121.3113865323784</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K11" t="n">
-        <v>4.76</v>
+        <v>2.94</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>133.4</v>
+        <v>130.95</v>
       </c>
       <c r="I12" t="n">
         <v>131.4151217659874</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
-        <v>9.029999999999999</v>
+        <v>7.03</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>135.95</v>
+        <v>138.45</v>
       </c>
       <c r="I13" t="n">
         <v>136.2526725890852</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.82</v>
+        <v>-5.73</v>
       </c>
       <c r="L13" t="n">
-        <v>4.12</v>
+        <v>7.94</v>
       </c>
       <c r="M13" t="n">
         <v>0.08</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.65</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>138.15</v>
+        <v>136.65</v>
       </c>
       <c r="I14" t="n">
         <v>137.4673360156675</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.22</v>
+        <v>-1.3</v>
       </c>
       <c r="L14" t="n">
         <v>3.36</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.22</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>138.7</v>
+        <v>142.8</v>
       </c>
       <c r="I15" t="n">
         <v>140.7981270142535</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>5.34</v>
       </c>
       <c r="M15" t="n">
         <v>0.91</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="O15" t="n">
         <v>-2.29</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>154.45</v>
+        <v>150.55</v>
       </c>
       <c r="I16" t="n">
         <v>152.4281942401249</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>8.16</v>
+        <v>5.43</v>
       </c>
       <c r="L16" t="n">
         <v>4.06</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44967.55208333334</v>
+        <v>44970.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>149.25</v>
+        <v>159.55</v>
       </c>
       <c r="I17" t="n">
         <v>155.8446729094282</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.86</v>
+        <v>-5.98</v>
       </c>
       <c r="L17" t="n">
-        <v>3.65</v>
+        <v>7.41</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5</v>
+        <v>4.96</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>8.51</v>
       </c>
       <c r="O17" t="n">
         <v>-5.2</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.32</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44999.38541666666</v>
+        <v>44999.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>168.4</v>
+        <v>165.6</v>
       </c>
       <c r="I18" t="n">
         <v>167.7773348079699</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>5.55</v>
+        <v>3.79</v>
       </c>
       <c r="L18" t="n">
         <v>2.44</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>174.3</v>
+        <v>177.25</v>
       </c>
       <c r="I19" t="n">
         <v>177.0460037299829</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.25</v>
+        <v>-7.04</v>
       </c>
       <c r="L19" t="n">
         <v>8.699999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>173.7</v>
+        <v>172</v>
       </c>
       <c r="I20" t="n">
         <v>172.1582541907497</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>-2</v>
+        <v>-2.96</v>
       </c>
       <c r="L20" t="n">
         <v>5.81</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45112.38541666666</v>
+        <v>45112.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>165.15</v>
+        <v>167.35</v>
       </c>
       <c r="I21" t="n">
         <v>167.2897471657512</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>3.98</v>
+        <v>2.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45163.55208333334</v>
+        <v>45166.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>188.05</v>
+        <v>185.25</v>
       </c>
       <c r="I22" t="n">
         <v>186.6444653055603</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>12.37</v>
+        <v>10.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.49</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.66</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45187.38541666666</v>
+        <v>45187.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>190.45</v>
+        <v>190.6</v>
       </c>
       <c r="I23" t="n">
         <v>190.4896393292011</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.81</v>
+        <v>-2.89</v>
       </c>
       <c r="L23" t="n">
         <v>6.05</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>207.95</v>
+        <v>204.65</v>
       </c>
       <c r="I24" t="n">
         <v>207.0652516902791</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>9.1</v>
+        <v>7.37</v>
       </c>
       <c r="L24" t="n">
         <v>4.38</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.41</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>208.45</v>
+        <v>214.65</v>
       </c>
       <c r="I25" t="n">
         <v>212.7489912813774</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.86</v>
+        <v>-4.89</v>
       </c>
       <c r="L25" t="n">
         <v>5.55</v>
@@ -1866,7 +2165,7 @@
         <v>2.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>-5.23</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.85</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45252.55208333334</v>
+        <v>45253.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>201.95</v>
+        <v>199.95</v>
       </c>
       <c r="I26" t="n">
         <v>201.5724854359187</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.92</v>
+        <v>-6.85</v>
       </c>
       <c r="L26" t="n">
-        <v>6.03</v>
+        <v>7.62</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>206.65</v>
+        <v>217.45</v>
       </c>
       <c r="I27" t="n">
         <v>210.4109465635566</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.35</v>
+        <v>-8.75</v>
       </c>
       <c r="L27" t="n">
-        <v>4.85</v>
+        <v>11.85</v>
       </c>
       <c r="M27" t="n">
-        <v>0.93</v>
+        <v>1.79</v>
       </c>
       <c r="N27" t="n">
-        <v>3.96</v>
+        <v>5.76</v>
       </c>
       <c r="O27" t="n">
         <v>-0.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.51</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45365.55208333334</v>
+        <v>45366.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>386.65</v>
+        <v>354.1</v>
       </c>
       <c r="I28" t="n">
         <v>379.5070745304799</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K28" t="n">
-        <v>77.81</v>
+        <v>62.84</v>
       </c>
       <c r="L28" t="n">
         <v>5.38</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>19.24</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45384.38541666666</v>
+        <v>45384.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>411.45</v>
+        <v>420.15</v>
       </c>
       <c r="I29" t="n">
         <v>413.4338503304928</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-16.2</v>
+        <v>-18.65</v>
       </c>
       <c r="L29" t="n">
-        <v>18.57</v>
+        <v>19.56</v>
       </c>
       <c r="M29" t="n">
         <v>1.75</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.15</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45442.38541666666</v>
+        <v>45442.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>428.3</v>
+        <v>418.65</v>
       </c>
       <c r="I30" t="n">
         <v>418.7929082245474</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>57.83333333333334</v>
+        <v>58</v>
       </c>
       <c r="K30" t="n">
-        <v>1.94</v>
+        <v>-0.36</v>
       </c>
       <c r="L30" t="n">
         <v>6.59</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.71</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>439.75</v>
+        <v>451.85</v>
       </c>
       <c r="I31" t="n">
         <v>444.7973021019927</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.04</v>
+        <v>-7.93</v>
       </c>
       <c r="L31" t="n">
         <v>9.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.36</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>556.5</v>
+        <v>540.5</v>
       </c>
       <c r="I32" t="n">
         <v>552.8998395368211</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>23.16</v>
+        <v>19.62</v>
       </c>
       <c r="L32" t="n">
         <v>3.59</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>15.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>610.45</v>
+        <v>642.95</v>
       </c>
       <c r="I33" t="n">
         <v>618.3621146909483</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-12.94</v>
+        <v>-18.95</v>
       </c>
       <c r="L33" t="n">
-        <v>15.62</v>
+        <v>21.35</v>
       </c>
       <c r="M33" t="n">
         <v>3.01</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.11</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45539.38541666666</v>
+        <v>45539.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>705.5</v>
+        <v>683.5</v>
       </c>
       <c r="I34" t="n">
         <v>690.4947826049809</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>9.73</v>
+        <v>6.31</v>
       </c>
       <c r="L34" t="n">
         <v>4.94</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>495.45</v>
+        <v>524.8</v>
       </c>
       <c r="I35" t="n">
         <v>508.8783537920694</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>27.51</v>
+        <v>23.22</v>
       </c>
       <c r="L35" t="n">
         <v>3.4</v>
@@ -2436,7 +2855,7 @@
         <v>2.12</v>
       </c>
       <c r="N35" t="n">
-        <v>5.19</v>
+        <v>5.9</v>
       </c>
       <c r="O35" t="n">
         <v>-6.1</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>11.51</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>495.85</v>
+        <v>478.45</v>
       </c>
       <c r="I36" t="n">
         <v>480.5144998693209</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.52</v>
+        <v>-8.83</v>
       </c>
       <c r="L36" t="n">
-        <v>6.08</v>
+        <v>9.18</v>
       </c>
       <c r="M36" t="n">
         <v>0.79</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>3.86</v>
       </c>
       <c r="O36" t="n">
         <v>5.9</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>11.98</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>508</v>
+        <v>517.65</v>
       </c>
       <c r="I37" t="n">
         <v>516.2036638435796</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.18</v>
+        <v>-8.19</v>
       </c>
       <c r="L37" t="n">
-        <v>6.5</v>
+        <v>9.68</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7</v>
+        <v>2.06</v>
       </c>
       <c r="N37" t="n">
         <v>4.53</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>487.8</v>
+        <v>473.35</v>
       </c>
       <c r="I38" t="n">
         <v>477.4951397212264</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.77</v>
+        <v>-8.56</v>
       </c>
       <c r="L38" t="n">
-        <v>7.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>1.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.66</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>435.6</v>
+        <v>458.8</v>
       </c>
       <c r="I39" t="n">
         <v>448.2493218703002</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>7.98</v>
+        <v>3.07</v>
       </c>
       <c r="L39" t="n">
         <v>3.94</v>
@@ -2664,7 +3131,7 @@
         <v>0.86</v>
       </c>
       <c r="N39" t="n">
-        <v>2.82</v>
+        <v>6.52</v>
       </c>
       <c r="O39" t="n">
         <v>-2.79</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>9.09</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>455.05</v>
+        <v>447.85</v>
       </c>
       <c r="I40" t="n">
         <v>450.3288920684232</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.82</v>
+        <v>-2.39</v>
       </c>
       <c r="L40" t="n">
         <v>5.07</v>
       </c>
       <c r="M40" t="n">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="N40" t="n">
         <v>5.35</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>366.95</v>
+        <v>376.7</v>
       </c>
       <c r="I41" t="n">
         <v>374.9747142896649</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K41" t="n">
-        <v>18.06</v>
+        <v>15.89</v>
       </c>
       <c r="L41" t="n">
         <v>4.95</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>386.4</v>
+        <v>358.9</v>
       </c>
       <c r="I42" t="n">
         <v>375.810468268905</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K42" t="n">
-        <v>2.57</v>
+        <v>-4.73</v>
       </c>
       <c r="L42" t="n">
-        <v>2.28</v>
+        <v>4.95</v>
       </c>
       <c r="M42" t="n">
-        <v>0.44</v>
+        <v>1.14</v>
       </c>
       <c r="N42" t="n">
-        <v>2.27</v>
+        <v>7.08</v>
       </c>
       <c r="O42" t="n">
         <v>2.34</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.19</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>367.7</v>
+        <v>373.25</v>
       </c>
       <c r="I43" t="n">
         <v>369.8700399616103</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.45</v>
+        <v>-4</v>
       </c>
       <c r="L43" t="n">
         <v>7.24</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>427</v>
+        <v>420.95</v>
       </c>
       <c r="I44" t="n">
         <v>421.6427339774971</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K44" t="n">
-        <v>14.4</v>
+        <v>12.78</v>
       </c>
       <c r="L44" t="n">
         <v>1.88</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>437.05</v>
+        <v>465.9</v>
       </c>
       <c r="I45" t="n">
         <v>441.784985112265</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.82</v>
+        <v>-10.68</v>
       </c>
       <c r="L45" t="n">
-        <v>4.81</v>
+        <v>11.18</v>
       </c>
       <c r="M45" t="n">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="N45" t="n">
-        <v>2.15</v>
+        <v>6.78</v>
       </c>
       <c r="O45" t="n">
         <v>-0.91</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.89</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>472.7</v>
+        <v>450.65</v>
       </c>
       <c r="I46" t="n">
         <v>454.5317712940495</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>1.46</v>
+        <v>-3.27</v>
       </c>
       <c r="L46" t="n">
         <v>5.01</v>
       </c>
       <c r="M46" t="n">
-        <v>-0</v>
+        <v>1.84</v>
       </c>
       <c r="N46" t="n">
-        <v>1.72</v>
+        <v>5.48</v>
       </c>
       <c r="O46" t="n">
         <v>6.78</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.92</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>448.05</v>
+        <v>454.7</v>
       </c>
       <c r="I47" t="n">
         <v>451.880974632354</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>0.58</v>
+        <v>-0.9</v>
       </c>
       <c r="L47" t="n">
         <v>3.35</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>438.15</v>
+        <v>434.9</v>
       </c>
       <c r="I48" t="n">
         <v>436.007859543377</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.64</v>
+        <v>-4.35</v>
       </c>
       <c r="L48" t="n">
-        <v>3.84</v>
+        <v>4.76</v>
       </c>
       <c r="M48" t="n">
         <v>0.82</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.72</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>404.6</v>
+        <v>410</v>
       </c>
       <c r="I49" t="n">
         <v>406.8215906304576</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>56</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>6.97</v>
+        <v>5.73</v>
       </c>
       <c r="L49" t="n">
         <v>3.36</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.74</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>425.9</v>
+        <v>419.05</v>
       </c>
       <c r="I50" t="n">
         <v>423.3759543067795</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>3.88</v>
+        <v>2.21</v>
       </c>
       <c r="L50" t="n">
         <v>2.06</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>405.3</v>
+        <v>411.55</v>
       </c>
       <c r="I51" t="n">
         <v>411.2916748687957</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K51" t="n">
-        <v>3.28</v>
+        <v>1.79</v>
       </c>
       <c r="L51" t="n">
         <v>1.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>3.8</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>418.95</v>
+        <v>409.35</v>
       </c>
       <c r="I52" t="n">
         <v>411.4694840450875</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>1.8</v>
+        <v>-0.53</v>
       </c>
       <c r="L52" t="n">
         <v>2.54</v>
       </c>
       <c r="M52" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="N52" t="n">
-        <v>1.86</v>
+        <v>2.74</v>
       </c>
       <c r="O52" t="n">
         <v>1.26</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.04</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>425.5</v>
+        <v>441.85</v>
       </c>
       <c r="I53" t="n">
         <v>430.5119294137216</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.95</v>
+        <v>-7.94</v>
       </c>
       <c r="L53" t="n">
-        <v>4.28</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.83</v>
+        <v>5.64</v>
       </c>
       <c r="O53" t="n">
         <v>-2.74</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.47</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46042.38541666666</v>
+        <v>46042.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>431.6</v>
+        <v>427.15</v>
       </c>
       <c r="I54" t="n">
         <v>431.2556479383083</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.32</v>
+        <v>-3.33</v>
       </c>
       <c r="L54" t="n">
         <v>3.68</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.46</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>449</v>
+        <v>485.25</v>
       </c>
       <c r="I55" t="n">
         <v>459.0201178290175</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.12</v>
+        <v>-13.6</v>
       </c>
       <c r="L55" t="n">
-        <v>5.43</v>
+        <v>15.18</v>
       </c>
       <c r="M55" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="N55" t="n">
-        <v>2.98</v>
+        <v>9.76</v>
       </c>
       <c r="O55" t="n">
         <v>-1.82</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46065.55208333334</v>
+        <v>46066.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>473.55</v>
+        <v>461.15</v>
       </c>
       <c r="I56" t="n">
         <v>473.2419722051528</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.41</v>
+        <v>-4.97</v>
       </c>
       <c r="L56" t="n">
-        <v>6.34</v>
+        <v>6.79</v>
       </c>
       <c r="M56" t="n">
         <v>2.28</v>
       </c>
       <c r="N56" t="n">
-        <v>3.58</v>
+        <v>4.12</v>
       </c>
       <c r="O56" t="n">
         <v>9.76</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>473</v>
+        <v>486.55</v>
       </c>
       <c r="I57" t="n">
         <v>483.7256320084942</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.57</v>
+        <v>-5.51</v>
       </c>
       <c r="L57" t="n">
-        <v>5.42</v>
+        <v>6.02</v>
       </c>
       <c r="M57" t="n">
         <v>2.59</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.72</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>471.15</v>
+        <v>457.2</v>
       </c>
       <c r="I58" t="n">
         <v>458.8974524807055</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.17</v>
+        <v>-6.03</v>
       </c>
       <c r="L58" t="n">
-        <v>5.3</v>
+        <v>6.61</v>
       </c>
       <c r="M58" t="n">
         <v>0.06</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.73</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>477.9</v>
+        <v>491.5</v>
       </c>
       <c r="I59" t="n">
         <v>487.5835599534931</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.53</v>
+        <v>-7.5</v>
       </c>
       <c r="L59" t="n">
-        <v>7.72</v>
+        <v>8.76</v>
       </c>
       <c r="M59" t="n">
         <v>1.09</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>4.06</v>
       </c>
       <c r="O59" t="n">
         <v>-2.29</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.94</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>478</v>
+        <v>467.5</v>
       </c>
       <c r="I60" t="n">
         <v>470.6081059209831</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.75</v>
+        <v>-4.88</v>
       </c>
       <c r="L60" t="n">
         <v>5.66</v>
       </c>
       <c r="M60" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="N60" t="n">
-        <v>2.95</v>
+        <v>5.63</v>
       </c>
       <c r="O60" t="n">
         <v>4.06</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>7.21</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>455.3</v>
+        <v>489.5</v>
       </c>
       <c r="I61" t="n">
         <v>480.5410352620613</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K61" t="n">
-        <v>2.61</v>
+        <v>-4.71</v>
       </c>
       <c r="L61" t="n">
-        <v>1.91</v>
+        <v>6.82</v>
       </c>
       <c r="M61" t="n">
-        <v>0.75</v>
+        <v>3.67</v>
       </c>
       <c r="N61" t="n">
-        <v>0.42</v>
+        <v>7.58</v>
       </c>
       <c r="O61" t="n">
         <v>-5.63</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.01</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>486.9</v>
+        <v>483.45</v>
       </c>
       <c r="I62" t="n">
         <v>484.5256523670053</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.53</v>
+        <v>-1.24</v>
       </c>
       <c r="L62" t="n">
         <v>3.65</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.74</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>425.7</v>
+        <v>431.5</v>
       </c>
       <c r="I63" t="n">
         <v>429.1708610453895</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>43.83333333333334</v>
+        <v>44</v>
       </c>
       <c r="K63" t="n">
-        <v>11.95</v>
+        <v>10.75</v>
       </c>
       <c r="L63" t="n">
         <v>2.69</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.13</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>488.05</v>
+        <v>477.5</v>
       </c>
       <c r="I64" t="n">
         <v>480.3390535512873</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>70</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>13.11</v>
+        <v>10.66</v>
       </c>
       <c r="L64" t="n">
         <v>2.48</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>54</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.74</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.79</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.63</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.81</v>
+        <v>62.84</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.29</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.85</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7198,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.57</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -6431,7 +7218,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.79</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.69</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
